--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342D4401-E53F-4FB4-853D-1ADAE2C30F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,92 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Common</t>
+  </si>
+  <si>
+    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Product</t>
+  </si>
+  <si>
+    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Document</t>
+  </si>
+  <si>
+    <t>old,temp</t>
+  </si>
+  <si>
+    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\license.txt</t>
+  </si>
+  <si>
+    <t>Common</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>含める形式</t>
+    <rPh sb="0" eb="1">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>除外する形式</t>
+    <rPh sb="0" eb="2">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケイシキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>格納先</t>
+    <rPh sb="0" eb="2">
+      <t>カクノウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取得元（フルパス）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,11 +133,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +420,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.3984375" customWidth="1"/>
+    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342D4401-E53F-4FB4-853D-1ADAE2C30F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF0A45E-268A-4D7C-A737-3C9C7427912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,26 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Common</t>
-  </si>
-  <si>
-    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Product</t>
-  </si>
-  <si>
-    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\Document</t>
-  </si>
-  <si>
-    <t>old,temp</t>
-  </si>
-  <si>
-    <t>C:\Users\xxx\SharePoint\PackageMaster\Master\license.txt</t>
-  </si>
-  <si>
-    <t>Common</t>
-    <phoneticPr fontId="2"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -81,6 +62,14 @@
   </si>
   <si>
     <t>取得元（フルパス）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>C:\Users\ishid\Desktop\project_management\tool\package-generator\test</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ggg\Common</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -421,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
@@ -432,65 +421,33 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="36">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF0A45E-268A-4D7C-A737-3C9C7427912A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D53F6E5-9571-4CEF-ADB3-EE8CFD3EE9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,11 +65,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>C:\Users\ishid\Desktop\project_management\tool\package-generator\test</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ggg\Common</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>.\test</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -436,17 +436,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="36">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D53F6E5-9571-4CEF-ADB3-EE8CFD3EE9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B3B05-23C4-432A-8E49-898D3F09C25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>.\test</t>
+    <t>.\A</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>

--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4B3B05-23C4-432A-8E49-898D3F09C25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469D682F-660E-40E8-91AB-11B365A8D526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -62,10 +62,6 @@
   </si>
   <si>
     <t>取得元（フルパス）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ggg\Common</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -102,12 +98,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,13 +124,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -423,7 +428,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -441,13 +446,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469D682F-660E-40E8-91AB-11B365A8D526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5D6B31-5C2F-4A50-BE97-5F04781FB106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="テンプレート" sheetId="1" r:id="rId1"/>
+    <sheet name="コースA" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,9 +26,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
   <si>
     <t>No</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取得元（フルパス）</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -58,10 +63,6 @@
     <rPh sb="2" eb="3">
       <t>サキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>取得元（フルパス）</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -415,11 +416,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.3984375" customWidth="1"/>
     <col min="4" max="4" width="21.59765625" customWidth="1"/>
   </cols>
@@ -429,16 +430,50 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75150BA2-5956-4186-B987-ACE3C5F8C674}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.3984375" customWidth="1"/>
+    <col min="4" max="4" width="21.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -455,4 +490,257 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
+    <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <xsd:import namespace="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a016a34-9640-43fb-86ea-5daabefdfe7e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4f27f6d2-b90d-46ae-b7ea-1d0a9165af30" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2d3c347e-deae-4f57-8eaf-3772dd4433c8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{7d33402d-c4f5-4775-814b-bfad88eb8e27}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2d3c347e-deae-4f57-8eaf-3772dd4433c8">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a016a34-9640-43fb-86ea-5daabefdfe7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2d3c347e-deae-4f57-8eaf-3772dd4433c8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
+    <ds:schemaRef ds:uri="2d3c347e-deae-4f57-8eaf-3772dd4433c8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tool/package-generator/config/package_definition.xlsx
+++ b/tool/package-generator/config/package_definition.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\package-generator\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\package-generator\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5D6B31-5C2F-4A50-BE97-5F04781FB106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7448288E-E729-4371-B32A-30E5E391C178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <t>No</t>
     <phoneticPr fontId="2"/>
@@ -63,10 +63,6 @@
     <rPh sb="2" eb="3">
       <t>サキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>.\A</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -477,12 +473,8 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
@@ -493,15 +485,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003F084FCF046B4A45A11E77E3180ECC70" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="93b3c00843758588d82b9b1cc445674f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a016a34-9640-43fb-86ea-5daabefdfe7e" xmlns:ns3="2d3c347e-deae-4f57-8eaf-3772dd4433c8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ba47e2a8c0ba124aa1c5a854c46141a" ns2:_="" ns3:_="">
     <xsd:import namespace="9a016a34-9640-43fb-86ea-5daabefdfe7e"/>
@@ -696,6 +679,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -708,14 +700,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143D2EB-8BE1-46FD-AA36-F0A52D61EC19}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -734,6 +718,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26368CF4-F3C0-43C6-B5BF-C4E959C1D0AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D39C44C-96D4-4F11-B752-6A8BD1FE27AD}">
   <ds:schemaRefs>
